--- a/artfynd/A 2633-2023 artfynd.xlsx
+++ b/artfynd/A 2633-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125058763</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2633-2023 artfynd.xlsx
+++ b/artfynd/A 2633-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125058763</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2633-2023 artfynd.xlsx
+++ b/artfynd/A 2633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125058763</v>
+        <v>122851868</v>
       </c>
       <c r="B2" t="n">
-        <v>57931</v>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477113</v>
+        <v>477099</v>
       </c>
       <c r="R2" t="n">
-        <v>6362860</v>
+        <v>6362789</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,8 +757,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,6 +788,681 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94824326</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>477146</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6362731</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102134604</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45033</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ängsmetallvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Adscita statices</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477146</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6362731</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94821602</v>
+      </c>
+      <c r="B5" t="n">
+        <v>29491</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102691</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Väddgökbi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nomada armata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Herrich-Schäffer, 1839</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477146</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6362731</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94821664</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43251</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102923</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477146</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6362731</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125058763</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6362860</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132811319</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6362860</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2633-2023 artfynd.xlsx
+++ b/artfynd/A 2633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94824326</v>
+        <v>134689209</v>
       </c>
       <c r="B3" t="n">
-        <v>45044</v>
+        <v>41643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102018</v>
+        <v>101532</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Piltecknad fältmätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Gagitodes sagittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477146</v>
+        <v>477120</v>
       </c>
       <c r="R3" t="n">
-        <v>6362731</v>
+        <v>6362947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,35 +906,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102134604</v>
+        <v>94824326</v>
       </c>
       <c r="B4" t="n">
-        <v>45033</v>
+        <v>45044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102366</v>
+        <v>102018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsmetallvinge</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adscita statices</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -984,12 +988,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94821602</v>
+        <v>102134604</v>
       </c>
       <c r="B5" t="n">
-        <v>29491</v>
+        <v>45033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,39 +1032,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102691</v>
+        <v>102366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Väddgökbi</t>
+          <t>Ängsmetallvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nomada armata</t>
+          <t>Adscita statices</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Herrich-Schäffer, 1839</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -1103,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,37 +1132,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94821664</v>
+        <v>94821602</v>
       </c>
       <c r="B6" t="n">
-        <v>43251</v>
+        <v>29491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102923</v>
+        <v>102691</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Väddgökbi</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Nomada armata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Herrich-Schäffer, 1839</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1177,7 +1173,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1255,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125058763</v>
+        <v>94821664</v>
       </c>
       <c r="B7" t="n">
-        <v>58238</v>
+        <v>43251</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>102923</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1760)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,27 +1284,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Komstad, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477113</v>
+        <v>477146</v>
       </c>
       <c r="R7" t="n">
-        <v>6362860</v>
+        <v>6362731</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,12 +1337,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1351,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,38 +1370,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132811319</v>
+        <v>125058763</v>
       </c>
       <c r="B8" t="n">
-        <v>101324</v>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222782</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1433,12 +1447,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1461,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,6 +1476,108 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132811319</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Komstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477113</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6362860</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2633-2023 artfynd.xlsx
+++ b/artfynd/A 2633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851868</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134689209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94824326</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102134604</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94821602</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94821664</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125058763</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,8 +1618,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811319</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>